--- a/audit/preuves/failles-et-correctifs.xlsx
+++ b/audit/preuves/failles-et-correctifs.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Failles et preuves" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Mode d'emploi" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="Protocole" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
-  <si>
-    <t>bibble-ai — failles constatées, preuves et correctifs</t>
-  </si>
-  <si>
-    <t>Chaque faille dispose d'un script qui l'exploite réellement. Le même script, rejoué après correction, doit échouer à l'exploiter : c'est la preuve. Les scripts s'exécutent sur une copie locale du site — jamais sur le site en ligne.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
+  <si>
+    <t>bibble-ai — failles, correctifs et preuves d'exécution</t>
+  </si>
+  <si>
+    <t>Démontrer chaque correctif par l'exécution : un script exploite la faille, le même script échoue à l'exploiter une fois le correctif appliqué. Exécution sur copie locale, sans toucher au site en ligne ni aux comptes Stripe et HeyGen.</t>
   </si>
   <si>
     <t>N°</t>
@@ -26,10 +26,10 @@
     <t>Faille</t>
   </si>
   <si>
-    <t>Ce qu'une personne peut en faire</t>
-  </si>
-  <si>
-    <t>Conséquence pour l'entreprise</t>
+    <t>Abus possible</t>
+  </si>
+  <si>
+    <t>Impact</t>
   </si>
   <si>
     <t>Gravité</t>
@@ -47,16 +47,16 @@
     <t>Commande à exécuter</t>
   </si>
   <si>
-    <t>Résultat attendu AVANT correctif</t>
+    <t>Attendu AVANT correctif</t>
   </si>
   <si>
     <t>Preuve AVANT</t>
   </si>
   <si>
-    <t>Correctif prévu</t>
-  </si>
-  <si>
-    <t>Résultat attendu APRÈS correctif</t>
+    <t>Correctif</t>
+  </si>
+  <si>
+    <t>Attendu APRÈS correctif</t>
   </si>
   <si>
     <t>Preuve APRÈS</t>
@@ -65,13 +65,13 @@
     <t>Statut</t>
   </si>
   <si>
-    <t>Un client peut s'attribuer des crédits gratuits</t>
-  </si>
-  <si>
-    <t>Toute personne inscrite peut, depuis la console de son navigateur et en une seule ligne, porter son solde à 9 999 crédits et passer son compte en plan Pro. Aucun outil ni compétence particulière n'est nécessaire : la clé qui le permet est publiée dans le code du site.</t>
-  </si>
-  <si>
-    <t>L'abonnement perd toute valeur : chacun peut générer autant de vidéos qu'il veut sans payer. Chaque vidéo produite est facturée à l'entreprise par HeyGen.</t>
+    <t>Attribution de crédits par l'utilisateur lui-même</t>
+  </si>
+  <si>
+    <t>Porter son solde à 9 999 crédits et passer en plan Pro depuis la console du navigateur, avec la clé publiée dans le code du site.</t>
+  </si>
+  <si>
+    <t>Vidéos illimitées sans paiement. Chaque vidéo produite est facturée par HeyGen.</t>
   </si>
   <si>
     <t>Critique</t>
@@ -89,16 +89,16 @@
     <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/01-rls-escalade-credits.mjs</t>
   </si>
   <si>
-    <t>❌ EXPLOITÉ — le solde passe de 2 à 9 999 crédits et le plan de « starter » à « pro » (code de sortie 1)</t>
-  </si>
-  <si>
-    <t>À exécuter — nécessite la base locale</t>
-  </si>
-  <si>
-    <t>Interdire au client de modifier lui-même les colonnes « crédits » et « plan » : seules les fonctions du serveur pourront y toucher.</t>
-  </si>
-  <si>
-    <t>✅ BLOQUÉ — 0 ligne modifiée, le solde reste à 2 crédits (code de sortie 0)</t>
+    <t>❌ Solde porté à 9 999 crédits, plan « pro » — code 1</t>
+  </si>
+  <si>
+    <t>À exécuter — base locale requise</t>
+  </si>
+  <si>
+    <t>Réserver la modification de « crédits » et « plan » au serveur.</t>
+  </si>
+  <si>
+    <t>✅ Modification refusée, solde inchangé — code 0</t>
   </si>
   <si>
     <t>En attente du correctif</t>
@@ -107,13 +107,13 @@
     <t>À corriger</t>
   </si>
   <si>
-    <t>Un client peut accéder aux vidéos d'un autre client</t>
-  </si>
-  <si>
-    <t>Un compte connecté peut demander le téléchargement ou le statut de la vidéo d'un autre client. Les deux routes concernées n'ont jamais vérifié à qui appartient la vidéo demandée.</t>
-  </si>
-  <si>
-    <t>Fuite de contenus clients : script publicitaire, avatar choisi, message commercial. Confidentialité rompue entre clients, y compris entre concurrents d'un même secteur.</t>
+    <t>Accès aux vidéos d'un autre client</t>
+  </si>
+  <si>
+    <t>Télécharger et suivre la vidéo d'un autre client à partir de son identifiant.</t>
+  </si>
+  <si>
+    <t>Fuite de contenus clients : script publicitaire, avatar, message commercial.</t>
   </si>
   <si>
     <t>Élevée</t>
@@ -131,25 +131,25 @@
     <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/02-idor-videos.mjs</t>
   </si>
   <si>
-    <t>❌ EXPLOITÉ — la demande portant sur la vidéo d'autrui reçoit la même réponse que sur sa propre vidéo : aucun refus (code de sortie 1)</t>
-  </si>
-  <si>
-    <t>À exécuter — nécessite la base locale et l'application lancée</t>
-  </si>
-  <si>
-    <t>Vérifier que la vidéo demandée appartient à la personne connectée, avant tout traitement et avant tout appel au prestataire vidéo.</t>
-  </si>
-  <si>
-    <t>✅ BLOQUÉ — les deux routes répondent « accès refusé » (403) (code de sortie 0)</t>
-  </si>
-  <si>
-    <t>Une notification de paiement rejouée crédite deux fois</t>
-  </si>
-  <si>
-    <t>Stripe renvoie automatiquement une notification lorsqu'il ne reçoit pas de confirmation — ce que l'application provoque elle-même en signalant une erreur. Chaque renvoi réattribue le plein montant de crédits du plan.</t>
-  </si>
-  <si>
-    <t>Des crédits distribués en double, voire en boucle, sans paiement correspondant. L'historique des crédits comporte des lignes fantômes : les comptes ne tombent plus juste.</t>
+    <t>❌ Réponses identiques sur sa vidéo et celle d'autrui — code 1</t>
+  </si>
+  <si>
+    <t>À exécuter — base locale et application requises</t>
+  </si>
+  <si>
+    <t>Vérifier la propriété de la vidéo avant tout traitement.</t>
+  </si>
+  <si>
+    <t>✅ Accès refusé (403) sur la vidéo d'autrui — code 0</t>
+  </si>
+  <si>
+    <t>Notification de paiement rejouée</t>
+  </si>
+  <si>
+    <t>Recevoir deux fois les crédits lorsque Stripe renvoie la notification — renvoi que l'application déclenche elle-même en signalant une erreur.</t>
+  </si>
+  <si>
+    <t>Crédits attribués sans paiement. Historique des crédits faussé.</t>
   </si>
   <si>
     <t>src/app/api/webhooks/stripe/route.ts:46-296</t>
@@ -164,22 +164,22 @@
     <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/03-idempotence-webhook.mjs</t>
   </si>
   <si>
-    <t>❌ EXPLOITÉ — le même événement envoyé deux fois produit 2 attributions de crédits au lieu d'une (code de sortie 1)</t>
-  </si>
-  <si>
-    <t>Enregistrer l'identifiant de chaque notification traitée et ignorer immédiatement toute répétition.</t>
-  </si>
-  <si>
-    <t>✅ BLOQUÉ — une seule attribution malgré le renvoi (code de sortie 0)</t>
-  </si>
-  <si>
-    <t>La date de début d'abonnement enregistrée est fausse</t>
-  </si>
-  <si>
-    <t>Ce n'est pas un abus volontaire mais une erreur de programmation : la date de début d'abonnement reçoit la date de fin. Toutes les périodes enregistrées durent donc zéro jour.</t>
-  </si>
-  <si>
-    <t>Impossible de savoir depuis quand un client est abonné. Tout calcul de renouvellement, de remboursement au prorata ou de relance repose sur une donnée fausse.</t>
+    <t>❌ 2 attributions de crédits pour 1 événement — code 1</t>
+  </si>
+  <si>
+    <t>Mémoriser les notifications traitées, ignorer les répétitions.</t>
+  </si>
+  <si>
+    <t>✅ 1 seule attribution malgré le renvoi — code 0</t>
+  </si>
+  <si>
+    <t>Date de début d'abonnement erronée</t>
+  </si>
+  <si>
+    <t>Aucun abus : erreur de programmation.</t>
+  </si>
+  <si>
+    <t>Périodes d'abonnement de durée nulle. Calculs de renouvellement et de prorata faussés.</t>
   </si>
   <si>
     <t>Moyenne</t>
@@ -197,28 +197,28 @@
     <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/04-periode-abonnement.mjs</t>
   </si>
   <si>
-    <t>❌ EXPLOITÉ — pour une période allant du 01/08 au 01/09, la fonction renvoie 01/09 comme début ET comme fin (code de sortie 1)</t>
-  </si>
-  <si>
-    <t>✔ Exécutée le 2026-08-04 — résultat conforme (aucun prérequis)</t>
-  </si>
-  <si>
-    <t>Utiliser la date de début là où la date de début est attendue.</t>
-  </si>
-  <si>
-    <t>✅ BLOQUÉ — début 01/08 et fin 01/09, deux dates distinctes (code de sortie 0)</t>
-  </si>
-  <si>
-    <t>Une référence tarifaire manquante fausse l'attribution des crédits</t>
-  </si>
-  <si>
-    <t>Les six tarifs sont reliés aux plans par une table de correspondance. Si une référence n'est pas renseignée, son entrée devient vide ; plusieurs références manquantes se remplacent alors les unes les autres et la table se mélange, sans le moindre signal.</t>
-  </si>
-  <si>
-    <t>Constaté à l'exécution : la table tombe à 4 entrées au lieu de 6 et l'entrée vide vaut 15 crédits, le quota du plan Pro. Un abonné Starter peut donc recevoir le quota Pro — ou, à l'inverse, un client payant ne rien recevoir pendant que le paiement est considéré comme traité.</t>
-  </si>
-  <si>
-    <t>src/lib/stripe.ts (PLAN_CREDITS) ; src/app/api/webhooks/stripe/route.ts:20-30</t>
+    <t>❌ Période du 01/08 au 01/09 → début = fin = 01/09 — code 1</t>
+  </si>
+  <si>
+    <t>✔ Exécutée le 2026-08-04 — conforme</t>
+  </si>
+  <si>
+    <t>Renseigner la date de début avec la date de début.</t>
+  </si>
+  <si>
+    <t>✅ Début 01/08, fin 01/09 — code 0</t>
+  </si>
+  <si>
+    <t>Table des tarifs incomplète</t>
+  </si>
+  <si>
+    <t>Aucun abus : défaut de construction déclenché par une référence tarifaire absente.</t>
+  </si>
+  <si>
+    <t>Constaté à l'exécution : 4 entrées au lieu de 6, entrée vide à 15 crédits. Un abonné Starter reçoit le quota Pro ; un tarif inconnu est accepté sans aucun crédit attribué.</t>
+  </si>
+  <si>
+    <t>src/lib/stripe.ts ; src/app/api/webhooks/stripe/route.ts:20-30</t>
   </si>
   <si>
     <t>B3.5</t>
@@ -230,25 +230,22 @@
     <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/05-mapping-price-ids.mjs</t>
   </si>
   <si>
-    <t>❌ EXPLOITÉ — 4 entrées au lieu de 6, l'entrée vide vaut 15 crédits ; un tarif inconnu obtient une réponse « traité » sans qu'aucun crédit ne soit attribué (code de sortie 1)</t>
-  </si>
-  <si>
-    <t>✔ Exécutée le 2026-08-04 — résultat conforme (volet « table de correspondance »)</t>
-  </si>
-  <si>
-    <t>Écarter les références vides à la construction de la table, et signaler bruyamment tout tarif inconnu au lieu de l'ignorer silencieusement.</t>
-  </si>
-  <si>
-    <t>✅ BLOQUÉ — aucune entrée vide dans la table, et un tarif inconnu déclenche une alerte (code de sortie 0)</t>
-  </si>
-  <si>
-    <t>Cinq vidéos peuvent être générées avec un seul crédit</t>
-  </si>
-  <si>
-    <t>En lançant plusieurs générations au même instant, toutes lisent le solde avant que la première ne l'ait diminué. Toutes passent le contrôle et toutes aboutissent. Avec 1 crédit, 5 requêtes simultanées produisent 5 vidéos.</t>
-  </si>
-  <si>
-    <t>Chaque vidéo excédentaire est facturée à l'entreprise par le prestataire sans contrepartie. L'abus ne demande aucune compétence : il suffit de cliquer plusieurs fois.</t>
+    <t>❌ 4 entrées au lieu de 6, clé vide à 15 crédits — code 1</t>
+  </si>
+  <si>
+    <t>Écarter les entrées vides, signaler tout tarif inconnu.</t>
+  </si>
+  <si>
+    <t>✅ Aucune entrée vide, tarif inconnu signalé — code 0</t>
+  </si>
+  <si>
+    <t>Générations simultanées avec un seul crédit</t>
+  </si>
+  <si>
+    <t>Lancer cinq générations au même instant et obtenir cinq vidéos avec un crédit.</t>
+  </si>
+  <si>
+    <t>Vidéos excédentaires facturées sans contrepartie. Aucune compétence requise.</t>
   </si>
   <si>
     <t>src/app/api/generate-video/route.ts:98-181</t>
@@ -263,78 +260,76 @@
     <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/06-course-credits.mjs</t>
   </si>
   <si>
-    <t>❌ EXPLOITÉ — 5 vidéos lancées, 1 seul crédit débité, 4 vidéos offertes (code de sortie 1)</t>
-  </si>
-  <si>
-    <t>Débiter le crédit en une opération unique et indivisible en base, avant l'appel au prestataire, et le rembourser si la génération échoue.</t>
-  </si>
-  <si>
-    <t>✅ BLOQUÉ — 1 vidéo lancée, les 4 autres requêtes refusées (code de sortie 0)</t>
-  </si>
-  <si>
-    <t>Comment rejouer les preuves</t>
+    <t>❌ 5 vidéos lancées, 1 crédit débité — code 1</t>
+  </si>
+  <si>
+    <t>Débiter le crédit en une opération indivisible avant l'appel au prestataire, rembourser en cas d'échec.</t>
+  </si>
+  <si>
+    <t>✅ 1 vidéo lancée, 4 requêtes refusées — code 0</t>
+  </si>
+  <si>
+    <t>Protocole</t>
   </si>
   <si>
     <t>Principe</t>
   </si>
   <si>
-    <t>Chaque faille est exploitée pour de bon par un script. Le script se termine par « ❌ EXPLOITÉ » tant que la faille est présente, et par « ✅ BLOQUÉ » une fois le correctif appliqué. La preuve tient dans ce basculement, obtenu avec exactement la même commande.</t>
-  </si>
-  <si>
-    <t>Où cela s'exécute</t>
-  </si>
-  <si>
-    <t>Sur une copie du site installée sur un poste de travail, avec une base de données vierge créée à partir des fichiers du projet. Ni le site en ligne, ni la base réelle, ni le compte Stripe ne sont sollicités : un garde-fou dans les scripts refuse toute cible autre que locale.</t>
-  </si>
-  <si>
-    <t>Aucun compte tiers requis</t>
-  </si>
-  <si>
-    <t>Les notifications de paiement sont fabriquées et signées localement. Aucune vidéo n'est commandée au prestataire, donc aucune facturation n'est déclenchée par les tests.</t>
+    <t>Exploiter la faille avant correctif, échouer à l'exploiter après. Même commande, deux résultats.</t>
+  </si>
+  <si>
+    <t>Portée</t>
+  </si>
+  <si>
+    <t>Base locale créée depuis les fichiers du projet. Ni le site en ligne, ni la base réelle, ni le compte Stripe ne sont sollicités.</t>
+  </si>
+  <si>
+    <t>Comptes tiers</t>
+  </si>
+  <si>
+    <t>Aucun. Notifications de paiement signées localement, aucune vidéo commandée au prestataire.</t>
   </si>
   <si>
     <t>1. Préparer</t>
   </si>
   <si>
-    <t>npx supabase init puis npx supabase start — installe une base locale à partir des fichiers du projet. Copier audit/preuves/.env.preuves.example en .env.preuves et y coller les deux clés affichées.</t>
-  </si>
-  <si>
-    <t>2. Lancer le site en local</t>
+    <t>npx supabase init puis npx supabase start. Copier .env.preuves.example en .env.preuves, y coller les deux clés affichées.</t>
+  </si>
+  <si>
+    <t>2. Lancer l'application</t>
   </si>
   <si>
     <t>npm run dev, dans un second terminal.</t>
   </si>
   <si>
-    <t>3. Capturer l'état AVANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/run-all.mjs avant
-Les six scripts s'exécutent et leurs sorties horodatées sont archivées dans audit/preuves/resultats/avant/, avec un récapitulatif.</t>
+    <t>3. Capturer l'avant</t>
+  </si>
+  <si>
+    <t>run-all.mjs avant — sorties horodatées archivées dans resultats/avant/.</t>
   </si>
   <si>
     <t>4. Figer le point de départ</t>
   </si>
   <si>
-    <t>git tag preuve-avant — repère posé sur la version non corrigée, pour que la démonstration reste rejouable même après les correctifs.</t>
+    <t>git tag preuve-avant — conserver la version non corrigée, rejouable.</t>
   </si>
   <si>
     <t>5. Corriger</t>
   </si>
   <si>
-    <t>Les correctifs sont appliqués dans l'ordre du plan : d'abord les crédits gratuits, puis les crédits multiples, puis l'accès aux vidéos, puis les notifications de paiement.</t>
-  </si>
-  <si>
-    <t>6. Capturer l'état APRÈS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/run-all.mjs apres
-Les six lignes doivent être passées de ❌ à ✅. C'est le livrable de recette.</t>
-  </si>
-  <si>
-    <t>Lecture des résultats</t>
-  </si>
-  <si>
-    <t>Code 0 = ✅ la faille n'est plus exploitable. Code 1 = ❌ la faille est exploitable. Code 2 = ⚠️ le test n'a pas pu conclure (un prérequis manquait).</t>
+    <t>Appliquer les correctifs dans l'ordre du plan.</t>
+  </si>
+  <si>
+    <t>6. Capturer l'après</t>
+  </si>
+  <si>
+    <t>run-all.mjs apres — les six lignes doivent passer de ❌ à ✅.</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>0 = ✅ faille non exploitable. 1 = ❌ faille exploitable. 2 = ⚠️ prérequis manquant.</t>
   </si>
 </sst>
 </file>
@@ -893,17 +888,18 @@
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="10" width="46" customWidth="1"/>
-    <col min="11" max="11" width="34" customWidth="1"/>
-    <col min="12" max="12" width="46" customWidth="1"/>
-    <col min="13" max="13" width="42" customWidth="1"/>
-    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="9" max="9" width="46" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
+    <col min="13" max="13" width="40" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -992,7 +988,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="108" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1039,7 +1035,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" ht="108" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>2</v>
       </c>
@@ -1086,7 +1082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="108" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1133,7 +1129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="108" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>4</v>
       </c>
@@ -1180,7 +1176,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" ht="108" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -1212,13 +1208,13 @@
         <v>72</v>
       </c>
       <c r="K8" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="M8" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>75</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>29</v>
@@ -1227,45 +1223,45 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="108" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>6</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="D9" s="15" t="s">
         <v>77</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>78</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="H9" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="J9" s="18" t="s">
         <v>82</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>83</v>
       </c>
       <c r="K9" s="19" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="M9" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="N9" s="15" t="s">
         <v>29</v>
@@ -1297,89 +1293,89 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="26" t="s">
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="27" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="4" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
+      <c r="C4" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="28" t="s">
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="25" t="s">
+      <c r="C5" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="26" t="s">
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="27" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
+      <c r="C6" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="28" t="s">
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="26" t="s">
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="27" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
+      <c r="C8" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="28" t="s">
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="9" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="25" t="s">
+      <c r="C9" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="26" t="s">
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="27" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
+      <c r="C10" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="28" t="s">
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="25" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="11" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="25" t="s">
+      <c r="C11" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="26" t="s">
+    </row>
+    <row r="12" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="27" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="12" ht="58" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
+      <c r="C12" s="28" t="s">
         <v>105</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/audit/preuves/failles-et-correctifs.xlsx
+++ b/audit/preuves/failles-et-correctifs.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Failles et preuves" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Protocole" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="88">
   <si>
     <t>bibble-ai — failles, correctifs et preuves d'exécution</t>
   </si>
@@ -92,7 +91,7 @@
     <t>❌ Solde porté à 9 999 crédits, plan « pro » — code 1</t>
   </si>
   <si>
-    <t>À exécuter — base locale requise</t>
+    <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/01-rls-escalade-credits.log)</t>
   </si>
   <si>
     <t>Réserver la modification de « crédits » et « plan » au serveur.</t>
@@ -134,7 +133,7 @@
     <t>❌ Réponses identiques sur sa vidéo et celle d'autrui — code 1</t>
   </si>
   <si>
-    <t>À exécuter — base locale et application requises</t>
+    <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/02-idor-videos.log)</t>
   </si>
   <si>
     <t>Vérifier la propriété de la vidéo avant tout traitement.</t>
@@ -167,6 +166,9 @@
     <t>❌ 2 attributions de crédits pour 1 événement — code 1</t>
   </si>
   <si>
+    <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/03-idempotence-webhook.log)</t>
+  </si>
+  <si>
     <t>Mémoriser les notifications traitées, ignorer les répétitions.</t>
   </si>
   <si>
@@ -200,7 +202,7 @@
     <t>❌ Période du 01/08 au 01/09 → début = fin = 01/09 — code 1</t>
   </si>
   <si>
-    <t>✔ Exécutée le 2026-08-04 — conforme</t>
+    <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/04-periode-abonnement.log)</t>
   </si>
   <si>
     <t>Renseigner la date de début avec la date de début.</t>
@@ -233,6 +235,9 @@
     <t>❌ 4 entrées au lieu de 6, clé vide à 15 crédits — code 1</t>
   </si>
   <si>
+    <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/05-mapping-price-ids.log)</t>
+  </si>
+  <si>
     <t>Écarter les entrées vides, signaler tout tarif inconnu.</t>
   </si>
   <si>
@@ -263,80 +268,20 @@
     <t>❌ 5 vidéos lancées, 1 crédit débité — code 1</t>
   </si>
   <si>
+    <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/06-course-credits.log)</t>
+  </si>
+  <si>
     <t>Débiter le crédit en une opération indivisible avant l'appel au prestataire, rembourser en cas d'échec.</t>
   </si>
   <si>
     <t>✅ 1 vidéo lancée, 4 requêtes refusées — code 0</t>
-  </si>
-  <si>
-    <t>Protocole</t>
-  </si>
-  <si>
-    <t>Principe</t>
-  </si>
-  <si>
-    <t>Exploiter la faille avant correctif, échouer à l'exploiter après. Même commande, deux résultats.</t>
-  </si>
-  <si>
-    <t>Portée</t>
-  </si>
-  <si>
-    <t>Base locale créée depuis les fichiers du projet. Ni le site en ligne, ni la base réelle, ni le compte Stripe ne sont sollicités.</t>
-  </si>
-  <si>
-    <t>Comptes tiers</t>
-  </si>
-  <si>
-    <t>Aucun. Notifications de paiement signées localement, aucune vidéo commandée au prestataire.</t>
-  </si>
-  <si>
-    <t>1. Préparer</t>
-  </si>
-  <si>
-    <t>npx supabase init puis npx supabase start. Copier .env.preuves.example en .env.preuves, y coller les deux clés affichées.</t>
-  </si>
-  <si>
-    <t>2. Lancer l'application</t>
-  </si>
-  <si>
-    <t>npm run dev, dans un second terminal.</t>
-  </si>
-  <si>
-    <t>3. Capturer l'avant</t>
-  </si>
-  <si>
-    <t>run-all.mjs avant — sorties horodatées archivées dans resultats/avant/.</t>
-  </si>
-  <si>
-    <t>4. Figer le point de départ</t>
-  </si>
-  <si>
-    <t>git tag preuve-avant — conserver la version non corrigée, rejouable.</t>
-  </si>
-  <si>
-    <t>5. Corriger</t>
-  </si>
-  <si>
-    <t>Appliquer les correctifs dans l'ordre du plan.</t>
-  </si>
-  <si>
-    <t>6. Capturer l'après</t>
-  </si>
-  <si>
-    <t>run-all.mjs apres — les six lignes doivent passer de ❌ à ✅.</t>
-  </si>
-  <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>0 = ✅ faille non exploitable. 1 = ❌ faille exploitable. 2 = ⚠️ prérequis manquant.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -374,7 +319,8 @@
       <color rgb="FFC00000"/>
     </font>
     <font>
-      <color rgb="FF7F6000"/>
+      <b/>
+      <color rgb="FF2E7D32"/>
     </font>
     <font>
       <color rgb="FF2E7D32"/>
@@ -382,14 +328,6 @@
     <font>
       <b/>
       <color rgb="FFC00000"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF2E7D32"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1F3864"/>
     </font>
   </fonts>
   <fills count="7">
@@ -455,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -522,24 +460,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,13 +1034,13 @@
         <v>50</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>29</v>
@@ -1134,40 +1054,40 @@
         <v>4</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7" s="23" t="s">
         <v>62</v>
       </c>
+      <c r="K7" s="19" t="s">
+        <v>63</v>
+      </c>
       <c r="L7" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>29</v>
@@ -1181,40 +1101,40 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>62</v>
+        <v>73</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>29</v>
@@ -1228,40 +1148,40 @@
         <v>6</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M9" s="20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N9" s="15" t="s">
         <v>29</v>
@@ -1279,110 +1199,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="96" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="3" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>105</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>
--- a/audit/preuves/failles-et-correctifs.xlsx
+++ b/audit/preuves/failles-et-correctifs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="90">
   <si>
     <t>bibble-ai — failles, correctifs et preuves d'exécution</t>
   </si>
@@ -94,52 +94,58 @@
     <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/01-rls-escalade-credits.log)</t>
   </si>
   <si>
-    <t>Réserver la modification de « crédits » et « plan » au serveur.</t>
+    <t>Fait — 003_securisation_profiles.sql : UPDATE retiré au niveau table, rendu sur full_name et avatar_url uniquement. Crédits, plan et références Stripe réservés au serveur.</t>
   </si>
   <si>
     <t>✅ Modification refusée, solde inchangé — code 0</t>
   </si>
   <si>
+    <t>✔ 2026-08-04 18:44Z — code 0 (resultats/apres/01-rls-escalade-credits.log)</t>
+  </si>
+  <si>
+    <t>Corrigé</t>
+  </si>
+  <si>
+    <t>Accès aux vidéos d'un autre client</t>
+  </si>
+  <si>
+    <t>Télécharger et suivre la vidéo d'un autre client à partir de son identifiant.</t>
+  </si>
+  <si>
+    <t>Fuite de contenus clients : script publicitaire, avatar, message commercial.</t>
+  </si>
+  <si>
+    <t>Élevée</t>
+  </si>
+  <si>
+    <t>src/app/api/video-download/route.ts:53-102 ; src/app/api/video-status/route.ts:85-121</t>
+  </si>
+  <si>
+    <t>B2.1 / B2.2</t>
+  </si>
+  <si>
+    <t>02-idor-videos.mjs</t>
+  </si>
+  <si>
+    <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/02-idor-videos.mjs</t>
+  </si>
+  <si>
+    <t>❌ Réponses identiques sur sa vidéo et celle d'autrui — code 1</t>
+  </si>
+  <si>
+    <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/02-idor-videos.log)</t>
+  </si>
+  <si>
+    <t>Vérifier la propriété de la vidéo avant tout traitement.</t>
+  </si>
+  <si>
+    <t>✅ Accès refusé (403) sur la vidéo d'autrui — code 0</t>
+  </si>
+  <si>
     <t>En attente du correctif</t>
   </si>
   <si>
     <t>À corriger</t>
-  </si>
-  <si>
-    <t>Accès aux vidéos d'un autre client</t>
-  </si>
-  <si>
-    <t>Télécharger et suivre la vidéo d'un autre client à partir de son identifiant.</t>
-  </si>
-  <si>
-    <t>Fuite de contenus clients : script publicitaire, avatar, message commercial.</t>
-  </si>
-  <si>
-    <t>Élevée</t>
-  </si>
-  <si>
-    <t>src/app/api/video-download/route.ts:53-102 ; src/app/api/video-status/route.ts:85-121</t>
-  </si>
-  <si>
-    <t>B2.1 / B2.2</t>
-  </si>
-  <si>
-    <t>02-idor-videos.mjs</t>
-  </si>
-  <si>
-    <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/02-idor-videos.mjs</t>
-  </si>
-  <si>
-    <t>❌ Réponses identiques sur sa vidéo et celle d'autrui — code 1</t>
-  </si>
-  <si>
-    <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/02-idor-videos.log)</t>
-  </si>
-  <si>
-    <t>Vérifier la propriété de la vidéo avant tout traitement.</t>
-  </si>
-  <si>
-    <t>✅ Accès refusé (403) sur la vidéo d'autrui — code 0</t>
   </si>
   <si>
     <t>Notification de paiement rejouée</t>
@@ -281,7 +287,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -324,6 +330,9 @@
     </font>
     <font>
       <color rgb="FF2E7D32"/>
+    </font>
+    <font>
+      <color rgb="FF7F6000"/>
     </font>
     <font>
       <b/>
@@ -393,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -428,7 +437,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -456,6 +465,15 @@
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -948,7 +966,7 @@
       <c r="M4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="10" t="s">
         <v>29</v>
       </c>
       <c r="O4" s="12" t="s">
@@ -995,11 +1013,11 @@
       <c r="M5" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="21" t="s">
-        <v>30</v>
+      <c r="N5" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1007,46 +1025,46 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>30</v>
+        <v>55</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1054,46 +1072,46 @@
         <v>4</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>59</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="21" t="s">
-        <v>30</v>
+        <v>67</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="O7" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1101,46 +1119,46 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>30</v>
+        <v>78</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1148,46 +1166,46 @@
         <v>6</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M9" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>30</v>
+        <v>89</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/audit/preuves/failles-et-correctifs.xlsx
+++ b/audit/preuves/failles-et-correctifs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
   <si>
     <t>bibble-ai — failles, correctifs et preuves d'exécution</t>
   </si>
@@ -136,16 +136,13 @@
     <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/02-idor-videos.log)</t>
   </si>
   <si>
-    <t>Vérifier la propriété de la vidéo avant tout traitement.</t>
+    <t>Fait — contrôle de propriété dans video-download et video-status : la vidéo doit appartenir à l'appelant, vérifié avant tout appel au prestataire. Message neutre, sans distinction entre vidéo inexistante et vidéo d'autrui.</t>
   </si>
   <si>
     <t>✅ Accès refusé (403) sur la vidéo d'autrui — code 0</t>
   </si>
   <si>
-    <t>En attente du correctif</t>
-  </si>
-  <si>
-    <t>À corriger</t>
+    <t>✔ 2026-08-04 19:01Z — code 0 (resultats/apres/02-idor-videos.log)</t>
   </si>
   <si>
     <t>Notification de paiement rejouée</t>
@@ -175,12 +172,15 @@
     <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/03-idempotence-webhook.log)</t>
   </si>
   <si>
-    <t>Mémoriser les notifications traitées, ignorer les répétitions.</t>
+    <t>Fait — table stripe_events (migration 005) : l'identifiant de chaque notification est enregistré avant traitement, un renvoi est acquitté sans retraitement. La réclamation est relâchée si le traitement échoue.</t>
   </si>
   <si>
     <t>✅ 1 seule attribution malgré le renvoi — code 0</t>
   </si>
   <si>
+    <t>✔ 2026-08-04 19:01Z — code 0 (resultats/apres/03-idempotence-webhook.log)</t>
+  </si>
+  <si>
     <t>Date de début d'abonnement erronée</t>
   </si>
   <si>
@@ -211,12 +211,15 @@
     <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/04-periode-abonnement.log)</t>
   </si>
   <si>
-    <t>Renseigner la date de début avec la date de début.</t>
+    <t>Fait — la date de début utilise current_period_start.</t>
   </si>
   <si>
     <t>✅ Début 01/08, fin 01/09 — code 0</t>
   </si>
   <si>
+    <t>✔ 2026-08-04 19:01Z — code 0 (resultats/apres/04-periode-abonnement.log)</t>
+  </si>
+  <si>
     <t>Table des tarifs incomplète</t>
   </si>
   <si>
@@ -244,12 +247,15 @@
     <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/05-mapping-price-ids.log)</t>
   </si>
   <si>
-    <t>Écarter les entrées vides, signaler tout tarif inconnu.</t>
+    <t>Fait — les tarifs non renseignés sont écartés de la table et signalés au démarrage. Un tarif inconnu déclenche une alerte et une réponse 202, distincte du 200 nominal dans le tableau de bord Stripe.</t>
   </si>
   <si>
     <t>✅ Aucune entrée vide, tarif inconnu signalé — code 0</t>
   </si>
   <si>
+    <t>✔ 2026-08-04 19:01Z — code 0 (resultats/apres/05-mapping-price-ids.log)</t>
+  </si>
+  <si>
     <t>Générations simultanées avec un seul crédit</t>
   </si>
   <si>
@@ -277,17 +283,20 @@
     <t>✔ 2026-08-04 18:30Z — code 1 (resultats/avant/06-course-credits.log)</t>
   </si>
   <si>
-    <t>Débiter le crédit en une opération indivisible avant l'appel au prestataire, rembourser en cas d'échec.</t>
+    <t>Fait — fonction consume_credit (migration 004) : le crédit est débité en une opération indivisible avant l'appel au prestataire, et remboursé si la génération échoue.</t>
   </si>
   <si>
     <t>✅ 1 vidéo lancée, 4 requêtes refusées — code 0</t>
+  </si>
+  <si>
+    <t>✔ 2026-08-04 19:01Z — code 0 (resultats/apres/06-course-credits.log)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -330,13 +339,6 @@
     </font>
     <font>
       <color rgb="FF2E7D32"/>
-    </font>
-    <font>
-      <color rgb="FF7F6000"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFC00000"/>
     </font>
   </fonts>
   <fills count="7">
@@ -402,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -464,16 +466,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1013,11 +1006,11 @@
       <c r="M5" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="21" t="s">
+      <c r="N5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="22" t="s">
-        <v>44</v>
+      <c r="O5" s="21" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1025,46 +1018,46 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="L6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="N6" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N6" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>44</v>
+      <c r="O6" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1080,7 +1073,7 @@
       <c r="D7" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="22" t="s">
         <v>59</v>
       </c>
       <c r="F7" s="17" t="s">
@@ -1107,11 +1100,11 @@
       <c r="M7" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="22" t="s">
-        <v>44</v>
+      <c r="N7" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7" s="21" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1119,46 +1112,46 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>44</v>
+        <v>79</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1166,46 +1159,46 @@
         <v>6</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M9" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="N9" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="O9" s="22" t="s">
-        <v>44</v>
+        <v>91</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/audit/preuves/failles-et-correctifs.xlsx
+++ b/audit/preuves/failles-et-correctifs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="105">
   <si>
     <t>bibble-ai — failles, correctifs et preuves d'exécution</t>
   </si>
@@ -290,6 +290,42 @@
   </si>
   <si>
     <t>✔ 2026-08-04 19:01Z — code 0 (resultats/apres/06-course-credits.log)</t>
+  </si>
+  <si>
+    <t>Contournement du contrôle de propriété des vidéos</t>
+  </si>
+  <si>
+    <t>Se déclarer propriétaire de la vidéo d'un autre client en insérant soi-même une ligne dans l'historique, ce que la policy d'insertion autorisait. Le contrôle ajouté pour la faille n° 2 est alors satisfait.</t>
+  </si>
+  <si>
+    <t>Le correctif de la faille n° 2 était neutralisable : les contenus des autres clients restaient accessibles.</t>
+  </si>
+  <si>
+    <t>supabase/migrations/001_initial_schema.sql:195-197</t>
+  </si>
+  <si>
+    <t>B2.5</t>
+  </si>
+  <si>
+    <t>07-rls-insertion-videos.mjs</t>
+  </si>
+  <si>
+    <t>node --env-file=audit/preuves/.env.preuves audit/preuves/scripts/07-rls-insertion-videos.mjs</t>
+  </si>
+  <si>
+    <t>❌ Insertion acceptée, la vidéo d'autrui redevient accessible — code 1</t>
+  </si>
+  <si>
+    <t>✔ 2026-08-04 20:58Z — code 1 (resultats/avant/07-rls-insertion-videos.log)</t>
+  </si>
+  <si>
+    <t>Fait — 007_revue_rls.sql : la policy d'insertion est retirée. Aucun code ne s'en servait, l'application insère avec la clé serveur. Revue des six tables consignée dans la migration.</t>
+  </si>
+  <si>
+    <t>✅ Insertion refusée, le refus 403 tient — code 0</t>
+  </si>
+  <si>
+    <t>✔ 2026-08-04 21:00Z — code 0 (resultats/apres/07-rls-insertion-videos.log)</t>
   </si>
 </sst>
 </file>
@@ -814,7 +850,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1201,8 +1237,55 @@
         <v>30</v>
       </c>
     </row>
+    <row r="10" ht="78" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:O9"/>
+  <autoFilter ref="A3:O10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
